--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39A.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t>49004</t>
   </si>
@@ -162,37 +162,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>DE53BB76C5848ED6A78A93D93428942E</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>5B30609E4D5F27A92B30B00120145ED3</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de julio del 2022 al 31 de diciembre del 2022 y con fundamento en los artículos 24, 25,26 y 27 de la Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala,  el Colegio de Bachilleres del Estado de Tlaxcala no emitió dictámenes sobre reserva o clasificación de información como confidencial.</t>
-  </si>
-  <si>
-    <t>54B233A41B2F976E0B7E4AADDE51C5A4</t>
-  </si>
-  <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>07/11/2022</t>
+    <t>Área de transparencia</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
+  </si>
+  <si>
+    <t>17/07/2023</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de enero del 2023 al 30 de junio del 2023 y con fundamento en los artículos 24, 25,26 y 27 de la Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala,  el Colegio de Bachilleres del Estado de Tlaxcala no emitió dictámenes sobre reserva o clasificación de información como confidencial.</t>
   </si>
   <si>
     <t>Ampliación de plazo</t>
@@ -621,10 +615,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -898,63 +892,10 @@
         <v>52</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -989,32 +930,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1029,17 +970,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1054,17 +995,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
